--- a/datafeed/biobrain_E4_S1_U1.xlsx
+++ b/datafeed/biobrain_E4_S1_U1.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5016" uniqueCount="1837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5016" uniqueCount="1838">
   <si>
     <t>examcode</t>
   </si>
@@ -5544,6 +5544,9 @@
   </si>
   <si>
     <t>Geographic distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">easy </t>
   </si>
 </sst>
 </file>
@@ -7675,7 +7678,7 @@
         <v>2</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>110</v>
+        <v>1837</v>
       </c>
       <c r="M2" s="6">
         <v>1</v>
